--- a/МК Куликова — большая таблица.xlsx
+++ b/МК Куликова — большая таблица.xlsx
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2 Расписание-сетка'!$A$4:$M$192</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'8 Открытые вопросы'!$A$4:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -17208,7 +17209,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -17858,7 +17859,338 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="17" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>ДР: цены и пакеты — актуальны ли пакеты по возрастам (6–9: 2000/2500; 10–17: 3000/3500; 18+: 3000–3500)? Как считали при 5+ (чаепитие), при выезде, при аренде кафе? Была ли доплата за именинника/торт/время?</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>взять её расчёт и последние 3–5 реальных ДР как примеры</t>
+        </is>
+      </c>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F25" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>ДР: минимальная группа и предоплата — сколько брали (30%? фикс?), как возвращали при отмене, были ли конфликты</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>закрепить правило письменно</t>
+        </is>
+      </c>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>ДР: какие студии подходят (стол под торт, место), какие нет; что просят родители чаще всего</t>
+        </is>
+      </c>
+      <c r="C27" s="17" t="inlineStr">
+        <is>
+          <t>список «ДР-локаций»</t>
+        </is>
+      </c>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F27" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>Педагоги: кто реально хорошо ведёт МК, кого не ставить; кого набирала сама — контакты и техники; кто ездит в другие студии</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>список с пометками</t>
+        </is>
+      </c>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>Заявки: откуда шли чаще (сайт/ВК/звонки/сертификаты/кафе); где хранились кроме таблицы; скрипт первого ответа</t>
+        </is>
+      </c>
+      <c r="C29" s="17" t="inlineStr">
+        <is>
+          <t>файлы</t>
+        </is>
+      </c>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F29" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>Сертификаты: макет, как учитывали, список выданных и непогашенных</t>
+        </is>
+      </c>
+      <c r="C30" s="17" t="inlineStr">
+        <is>
+          <t>файл</t>
+        </is>
+      </c>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F30" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>Кафе: до какого числа висело расписание, контакты, на чём остановились с каждым</t>
+        </is>
+      </c>
+      <c r="C31" s="17" t="inlineStr">
+        <is>
+          <t>статус по каждому кафе</t>
+        </is>
+      </c>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F31" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>Материалы: как закупали и доставляли, нормы на участника, остатки на складе/в офисе, себестоимость</t>
+        </is>
+      </c>
+      <c r="C32" s="17" t="inlineStr">
+        <is>
+          <t>расчёт</t>
+        </is>
+      </c>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F32" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>Отчётность: форма отчёта педагога после МК («скрипт куратора»), как считали ЗП педагогам за МК</t>
+        </is>
+      </c>
+      <c r="C33" s="17" t="inlineStr">
+        <is>
+          <t>файл</t>
+        </is>
+      </c>
+      <c r="D33" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>Стенды: размеры по студиям, исходники макетов (Canva/PSD), кто менял</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="inlineStr">
+        <is>
+          <t>файлы</t>
+        </is>
+      </c>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>Что бы поменяла первым делом; где были главные проблемы</t>
+        </is>
+      </c>
+      <c r="C35" s="17" t="inlineStr">
+        <is>
+          <t>совет</t>
+        </is>
+      </c>
+      <c r="D35" s="17" t="inlineStr">
+        <is>
+          <t>Мария</t>
+        </is>
+      </c>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>созвон</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="inlineStr">
+        <is>
+          <t>❓</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A4:F35"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/МК Куликова — большая таблица.xlsx
+++ b/МК Куликова — большая таблица.xlsx
@@ -29,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,8 +79,13 @@
       <color rgb="007D6C72"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9.5"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill/>
     </fill>
@@ -127,6 +132,11 @@
         <fgColor rgb="00F8E4EC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -154,7 +164,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -195,6 +205,27 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1153,344 +1184,576 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="60" customWidth="1" min="2" max="2"/>
-    <col width="38" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="44" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Правила модели «широкий выбор + гарантия от 2 человек»</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1">
+          <t>Как устроены мастер-классы: форматы и правила — простыми словами</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="15" t="inlineStr">
+        <is>
+          <t>Для тех, кто не в теме: сначала «что мы продаём» (4 формата), потом «как это работает» (7 правил), потом пример одной недели.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
-          <t>Правило</t>
+          <t>Блок</t>
         </is>
       </c>
       <c r="B4" s="12" t="inlineStr">
         <is>
-          <t>Как работает</t>
+          <t>Название</t>
         </is>
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Зачем</t>
+          <t>Что это простыми словами</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Кто отвечает</t>
+          <t>Пример</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
         <is>
+          <t>Кому и зачем</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>Цена и время</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="inlineStr">
+        <is>
+          <t>Кто ведёт / отвечает</t>
+        </is>
+      </c>
+      <c r="H4" s="12" t="inlineStr">
+        <is>
           <t>Статус</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>Одна тема на выходные</t>
-        </is>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>Каждые СБ–ВС одна картина для всех студий (масло/акрил). Темы меняются по неделям. Мастерская — одна тема на месяц.</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>Объединение групп без потерь; одна картинка и один референс на дату; одна закупка</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>Ангелина + Анастасия (темы)</t>
-        </is>
-      </c>
-      <c r="E5" s="13" t="inlineStr">
-        <is>
-          <t>🟡 согласовать</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>Сетка слотов</t>
-        </is>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>Студия: СБ 17:00 (мастерская 1–2 ч), ВС 17:00 (МК 3 ч). Хабы: + ВТ/ЧТ 19:00. Кафе: СБ 15:00–17:30. Время в студиях — после занятий.</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>Клиент видит 6–10 студий × дни × время = большой выбор</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>Ангелина</t>
-        </is>
-      </c>
-      <c r="E6" s="13" t="inlineStr">
+    <row r="5" ht="120" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>ЧТО ПРОДАЁМ</t>
+        </is>
+      </c>
+      <c r="B5" s="22" t="inlineStr">
+        <is>
+          <t>1. Мастер-класс «Картина за 3 часа»</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Основной продукт. Группа до 6 человек за 3 часа пишет одну и ту же картину маслом или акрилом по образцу (референсу). Педагог показывает этапы на своём холсте, каждый повторяет на своём. Уходят с готовой картиной 30×40. Опыт не нужен.</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>Воскресенье 11 октября, 17:00, студия Алтуфьево, тема «Домик в горах», масло. Записались 4 человека — МК состоится.</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="inlineStr">
+        <is>
+          <t>Взрослые и подростки 12+: отдохнуть, получить результат, фото. Пары, подруги, подарок по сертификату.</t>
+        </is>
+      </c>
+      <c r="F5" s="16" t="inlineStr">
+        <is>
+          <t>3500 ₽ (скетчинг/акварель — 2500). 3 часа. Все материалы включены. В студиях — по воскресеньям с 17:00 (после занятий).</t>
+        </is>
+      </c>
+      <c r="G5" s="16" t="inlineStr">
+        <is>
+          <t>Проверенный МК-педагог (Вересоцкая, Самбулова, Медков). Ангелина — набор, координация.</t>
+        </is>
+      </c>
+      <c r="H5" s="16" t="inlineStr">
+        <is>
+          <t>✅ продукт есть, расписание на согласовании</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="120" customHeight="1">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>ЧТО ПРОДАЁМ</t>
+        </is>
+      </c>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t>2. Мастерская выходного дня</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Короткое и недорогое занятие «руками» в своей студии: расписать шопер или кепку, собрать мозаику и т. п. Не картина по образцу — каждый делает свою вещь в одной технике. Тема одна на весь месяц, поэтому одна афиша на все субботы.</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Суббота 4 октября, 17:00, любая из 9 студий: роспись шоперов. Мама с ребёнком 6 лет приходят на 1 час, семья с подростком — на 2 часа.</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Семьи, дети от 4 лет, подростки, те, кому 3 часа/3500 не подходят. «Вход» в студию — потом на регулярные занятия или на МК.</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>1000 ₽ — 1 час (4–6 лет), 1500 ₽ — 2 часа (7+ и семьи). Заготовка включена. По субботам с 17:00 (Новаторская, Алтуфьево — 18:00; Зеленоград — пятница 18:00).</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>Педагог своей студии после занятий. Материалы — закупка студии.</t>
+        </is>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>🟡 идея Анастасии, цены и материалы не утверждены</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="120" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>ЧТО ПРОДАЁМ</t>
+        </is>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>3. Мастер-класс в кафе</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Тот же МК «Картина за 3 часа» (2–2,5 часа), но в кафе-партнёре: у них днём пусто, у нас студии заняты занятиями. Гость платит нам за МК и кафе — депозит на еду/напитки.</t>
+        </is>
+      </c>
+      <c r="D7" s="18" t="inlineStr">
+        <is>
+          <t>Суббота 15:00–17:30, ресторан «Бухара» у Ботанического сада, отдельная комната, 8 гостей, тема — та же, что в воскресенье в студиях.</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="inlineStr">
+        <is>
+          <t>Взрослые 18+, компании, свидания; кафе получает гостей, мы — дневной субботний слот и новую аудиторию.</t>
+        </is>
+      </c>
+      <c r="F7" s="18" t="inlineStr">
+        <is>
+          <t>2500–3000 ₽ + депозит кафе 1000–1500 ₽ (идёт кафе). До 12 человек. Суббота 15:00–17:30; возможно будни вечером.</t>
+        </is>
+      </c>
+      <c r="G7" s="18" t="inlineStr">
+        <is>
+          <t>Вересоцкая / Самбулова (свободны по СБ). Ангелина — договорённости с кафе.</t>
+        </is>
+      </c>
+      <c r="H7" s="18" t="inlineStr">
+        <is>
+          <t>🟡 кафе не подтверждены (связь потеряна месяц назад) — восстанавливаем</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="120" customHeight="1">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>ЧТО ПРОДАЁМ</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>4. Закрытые: ДР, девичник, корпоратив, индивидуально</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Компания бронирует МК под себя: любая дата и студия, своя тема, для ДР — стол под торт и чаепитие. Или один человек берёт педагога индивидуально в удобное время.</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>Пятница 19:00, Братиславская, ДР девочки 10 лет, 8 детей, акрил «Единорог», после — чай с тортом 40 минут.</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="inlineStr">
+        <is>
+          <t>Родители (ДР детей), подруги (девичник), HR (тимбилдинг), те, кому нужно «своё время».</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr">
+        <is>
+          <t>Пакеты по возрасту: 6–9 лет 2000–2500, 10–17 лет 3000–3500, 18+ 3000–3500 за человека; от 5 человек — чаепитие в подарок. Индивидуально 6000, пара 4500/чел. Любой день.</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr">
+        <is>
+          <t>Любой МК-педагог по договорённости. Цены ДР уточняем у Марии (предыдущий куратор).</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr">
+        <is>
+          <t>🟡 пакеты есть на бумаге, реальную практику уточняем</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="120" customHeight="1">
+      <c r="A9" s="26" t="inlineStr">
+        <is>
+          <t>КАК РАБОТАЕТ</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Правило 1. Одна тема на выходные</t>
+        </is>
+      </c>
+      <c r="C9" s="26" t="inlineStr">
+        <is>
+          <t>В одни выходные во всех студиях рисуют одну и ту же картину. Разнообразие — по неделям: на этой неделе «Домик в горах», на следующей — «Лунная ночь». Мастерская — одна тема на месяц.</t>
+        </is>
+      </c>
+      <c r="D9" s="26" t="inlineStr">
+        <is>
+          <t>11 октября во всех 9 студиях — «Домик в горах». 18 октября везде — «Тыквенный латте».</t>
+        </is>
+      </c>
+      <c r="E9" s="26" t="inlineStr">
+        <is>
+          <t>Если в двух соседних студиях по одному человеку — их можно объединить, потому что рисуют одно и то же. Одна картинка на афишу, один референс педагогам, одна закупка.</t>
+        </is>
+      </c>
+      <c r="F9" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="26" t="inlineStr">
+        <is>
+          <t>Темы предлагает Ангелина, утверждает Анастасия, на месяц вперёд.</t>
+        </is>
+      </c>
+      <c r="H9" s="26" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="inlineStr">
-        <is>
-          <t>Статусы слота</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>«идёт набор 1/6» → «состоится ✅» (2+) → «проведён» / «перенесён → куда». Видно на сайте и в штабе.</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
-        <is>
-          <t>Прозрачность для клиента и команды</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>Ангелина (штаб)</t>
-        </is>
-      </c>
-      <c r="E7" s="14" t="inlineStr">
-        <is>
-          <t>✅ в дашборде есть</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Правило Т-2 (48 часов)</t>
-        </is>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>&lt;2 записей за 48 ч → клиенту одно сообщение с 3 вариантами: (а) хаб кластера, то же время; (б) эта студия через неделю; (в) индивидуально 6000 / пара 4500. Клиент выбирает — запись переносится.</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
-        <is>
-          <t>Не отменяем, а переносим → клиент не теряется, экономика не рушится</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>Ангелина</t>
-        </is>
-      </c>
-      <c r="E8" s="13" t="inlineStr">
+    <row r="10" ht="120" customHeight="1">
+      <c r="A10" s="26" t="inlineStr">
+        <is>
+          <t>КАК РАБОТАЕТ</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Правило 2. Сетка слотов</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="inlineStr">
+        <is>
+          <t>У каждой студии постоянные «окна»: суббота 17:00 — мастерская, воскресенье 17:00 — МК. В трёх больших студиях (Отрадное 27, Братиславская, Алтуфьево) ещё будни 19:00. В кафе — суббота 15:00. Клиент выбирает студию и день, а не ждёт, когда «соберут группу».</t>
+        </is>
+      </c>
+      <c r="D10" s="26" t="inlineStr">
+        <is>
+          <t>Клиент из Отрадного видит: ВС 17:00 в Отрадном 27, ВС 17:00 в Отрадном 20к3, СБ 15:00 в «Бухаре», ЧТ 19:00 в Отрадном 27.</t>
+        </is>
+      </c>
+      <c r="E10" s="26" t="inlineStr">
+        <is>
+          <t>Большой выбор дат и мест — как у конкурентов (2–5 занятий в день), но по всем районам.</t>
+        </is>
+      </c>
+      <c r="F10" s="26" t="inlineStr">
+        <is>
+          <t>Время в студиях всегда после основных занятий.</t>
+        </is>
+      </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t>Ангелина ведёт сетку в штабе и на сайте.</t>
+        </is>
+      </c>
+      <c r="H10" s="26" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>Кластеры и хабы</t>
-        </is>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>Север: Отрадное 27, Отрадное 20к3, Алтуфьево, Яхромская → хаб Отрадное 27 / Алтуфьево. Восток: Братиславская, Новокосино, Перово → хаб Братиславская. Запад: Полежаевская. Юго-Запад: Новаторская. Зеленоград — отдельно.</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>Ехать ≤20 мин при объединении</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
+    <row r="11" ht="120" customHeight="1">
+      <c r="A11" s="26" t="inlineStr">
+        <is>
+          <t>КАК РАБОТАЕТ</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Правило 3. Статус слота виден всем</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t>У каждого окна есть статус: «идёт набор 1/6» → «состоится ✅» (когда 2 и больше) → «проведён» или «перенесён → куда». Статус видно на сайте и в штабе.</t>
+        </is>
+      </c>
+      <c r="D11" s="26" t="inlineStr">
+        <is>
+          <t>На сайте: «ВС 11.10 Алтуфьево — идёт набор 1/6». Через день: «состоится ✅ 3/6».</t>
+        </is>
+      </c>
+      <c r="E11" s="26" t="inlineStr">
+        <is>
+          <t>Клиент понимает, что происходит; команда видит, где нужен добор.</t>
+        </is>
+      </c>
+      <c r="F11" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="13" t="inlineStr">
+      <c r="G11" s="26" t="inlineStr">
+        <is>
+          <t>Ангелина обновляет ежедневно.</t>
+        </is>
+      </c>
+      <c r="H11" s="26" t="inlineStr">
+        <is>
+          <t>✅ в штабе есть</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="120" customHeight="1">
+      <c r="A12" s="26" t="inlineStr">
+        <is>
+          <t>КАК РАБОТАЕТ</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Правило 4. Проводим при 2+, за 48 часов решаем</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="inlineStr">
+        <is>
+          <t>МК проводим, если записались минимум 2 человека. Если за 2 дня до даты в окне 1 человек — не отменяем, а пишем ему одно сообщение с тремя вариантами: (а) тот же МК в той же теме в ближайшей большой студии в то же время; (б) тот же МК здесь через неделю; (в) индивидуально сейчас за 6000. Он выбирает — мы переносим запись.</t>
+        </is>
+      </c>
+      <c r="D12" s="26" t="inlineStr">
+        <is>
+          <t>В Яхромской на ВС записан 1 человек, в Отрадном 27 — 3. За 48 ч предлагаем ему Отрадное 27 (15 минут на метро) — он соглашается, в Отрадном становится 4.</t>
+        </is>
+      </c>
+      <c r="E12" s="26" t="inlineStr">
+        <is>
+          <t>Экономика: на 1 человека МК убыточен (педагогу 1500, выручка 3500), на 3 — маржа 8400. Клиент не теряется, потому что мы не отменяем, а предлагаем.</t>
+        </is>
+      </c>
+      <c r="F12" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G12" s="26" t="inlineStr">
+        <is>
+          <t>Ангелина (задача Т-2 подсвечивается в штабе автоматически).</t>
+        </is>
+      </c>
+      <c r="H12" s="26" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>Педагог на кластер</t>
-        </is>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>На выходные назначаем 3–4 МК-педагога (по кластеру). Если группы объединились — едет в хаб. Мастерскую ведёт педагог своей студии после занятий.</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>Мало проверенных МК-педагогов (3) — хватает на кластеры, не на 10 студий</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Анастасия (утверждает), Ангелина (согласует даты)</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
+    <row r="13" ht="120" customHeight="1">
+      <c r="A13" s="26" t="inlineStr">
+        <is>
+          <t>КАК РАБОТАЕТ</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Правило 5. Кластеры и хабы</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="inlineStr">
+        <is>
+          <t>Студии сгруппированы по районам, чтобы переезд при объединении был ≤20 минут. Север: Отрадное 27, Отрадное 20к3, Алтуфьево, Яхромская → собираем в Отрадном 27 или Алтуфьево (10 мольбертов). Восток: Братиславская, Новокосино, Перово → в Братиславской (новое большое помещение). Запад: Полежаевская. Юго-Запад: Новаторская. Зеленоград — сам по себе.</t>
+        </is>
+      </c>
+      <c r="D13" s="26" t="inlineStr">
+        <is>
+          <t>Новокосино 1 + Братиславская 2 → объединяем в Братиславской = 3.</t>
+        </is>
+      </c>
+      <c r="E13" s="26" t="inlineStr">
+        <is>
+          <t>Понятно, куда переносить, и кто едет.</t>
+        </is>
+      </c>
+      <c r="F13" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="26" t="inlineStr">
         <is>
           <t>🟡</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>Предоплата и перенос</t>
-        </is>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>Предоплата 500 ₽ при записи. Перенос без потерь за 24 ч. Менее 24 ч — предоплата сгорает. (Сейчас: 3 дня / −30% в день МК.)</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>Как у рынка; режет неявки</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Анастасия</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>🟡 менять правила сайта</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
-        <is>
-          <t>«Любое время» за деньги</t>
-        </is>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>Индивидуально 6000 (3 ч), пара 4500/чел, своя компания от 4 чел — 3500/чел в любой день и студию.</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>Закрывает запрос «хочу в четверг в 15:00» без риска</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>Анастасия (цены)</t>
-        </is>
-      </c>
-      <c r="E12" s="13" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
-        <is>
-          <t>Минимум и максимум</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Проводим при 2+. Максимум 6 (Алтуфьево, Братиславская — 8). Кафе — до 12.</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>По вместимости кабинетов</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
+    <row r="14" ht="120" customHeight="1">
+      <c r="A14" s="26" t="inlineStr">
+        <is>
+          <t>КАК РАБОТАЕТ</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>Правило 6. Педагог — на кластер</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="inlineStr">
+        <is>
+          <t>На выходные назначаем 3–4 МК-педагога, по одному на кластер, а не по одному на студию. Если группы объединились — педагог едет в хаб. Мастерскую в субботу ведёт педагог самой студии после своих занятий.</t>
+        </is>
+      </c>
+      <c r="D14" s="26" t="inlineStr">
+        <is>
+          <t>Вересоцкая — Север, Самбулова — Восток и Юго-Запад, Медков — Запад. В субботу в Яхромской мастерскую ведёт Медков у себя.</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="inlineStr">
+        <is>
+          <t>Проверенных МК-педагогов всего трое — на 10 студий не хватит, на 4 кластера хватит.</t>
+        </is>
+      </c>
+      <c r="F14" s="26" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
-        <is>
-          <t>✅</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Публикация</t>
-        </is>
-      </c>
-      <c r="B14" s="13" t="inlineStr">
-        <is>
-          <t>Расписание на месяц вперёд: темы по выходным + сетка. Стенд обновляем 1-го числа, статусы слотов на сайте — ежедневно.</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>Просьба Анастасии — раз в месяц</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>Ангелина + Дарья (СММ)</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>🟡</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Скорость ответа</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>Первый ответ ≤1 ч с конкретикой: 2–3 варианта дата/студия/цена. Напоминание через 48 ч.</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>Половина заявок раньше терялась из-за молчания</t>
-        </is>
-      </c>
-      <c r="D15" s="14" t="inlineStr">
-        <is>
-          <t>Ангелина / админ</t>
-        </is>
-      </c>
-      <c r="E15" s="14" t="inlineStr">
-        <is>
-          <t>✅ шаблоны готовы</t>
+      <c r="G14" s="26" t="inlineStr">
+        <is>
+          <t>Анастасия утверждает, Ангелина согласует даты напрямую.</t>
+        </is>
+      </c>
+      <c r="H14" s="26" t="inlineStr">
+        <is>
+          <t>🟡 педагоги не подтверждены</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
+      <c r="A15" s="26" t="inlineStr">
+        <is>
+          <t>КАК РАБОТАЕТ</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Правило 7. Предоплата и перенос</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>При записи — предоплата 500 ₽ (остальное на месте или по ссылке). Перенести можно без потерь, если предупредить за 24 часа; позже — предоплата сгорает. Кто хочет своё время и место — индивидуальный тариф.</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>Записалась в среду на воскресенье, внесла 500. В пятницу передумала — перенесли на следующее ВС без потерь.</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="inlineStr">
+        <is>
+          <t>Без предоплаты записываются и не приходят; правило «за 3 дня / минус 30% в день МК» — жёстче, чем у всех конкурентов.</t>
+        </is>
+      </c>
+      <c r="F15" s="26" t="inlineStr">
+        <is>
+          <t>Предоплата 500; индивидуально 6000; пара 4500/чел; компания от 4 — 3500/чел.</t>
+        </is>
+      </c>
+      <c r="G15" s="26" t="inlineStr">
+        <is>
+          <t>Анастасия (утвердить), админ (ссылки на оплату).</t>
+        </is>
+      </c>
+      <c r="H15" s="26" t="inlineStr">
+        <is>
+          <t>🟡 предложение</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>ПРИМЕР НЕДЕЛИ</t>
+        </is>
+      </c>
+      <c r="B16" s="28" t="inlineStr">
+        <is>
+          <t>Неделя 6–12 октября</t>
+        </is>
+      </c>
+      <c r="C16" s="14" t="inlineStr">
+        <is>
+          <t>Тема выходных — «Домик в горах» (масло). Мастерская месяца — роспись шоперов.</t>
+        </is>
+      </c>
+      <c r="D16" s="14" t="inlineStr">
+        <is>
+          <t>ЧТ 9.10 19:00 — МК в Отрадном 27 (будни, хаб). СБ 11.10 15:00 — МК в «Бухаре». СБ 17:00 — мастерская «шоперы» в 9 студиях. ВС 12.10 17:00 — МК «Домик в горах» в 9 студиях; за 48 ч смотрим набор: где 1 человек — предлагаем хаб кластера.</t>
+        </is>
+      </c>
+      <c r="E16" s="14" t="inlineStr">
+        <is>
+          <t>Клиент видит 12+ вариантов «куда пойти рисовать в эти выходные рядом с домом». Мы проводим только то, где 2+.</t>
+        </is>
+      </c>
+      <c r="F16" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr">
+        <is>
+          <t>Педагоги: Вересоцкая (Север + кафе), Самбулова (Восток/ЮЗ), Медков (Запад). Мастерские — педагоги студий.</t>
+        </is>
+      </c>
+      <c r="H16" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>

--- a/МК Куликова — большая таблица.xlsx
+++ b/МК Куликова — большая таблица.xlsx
@@ -609,10 +609,11 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20.09.2026 · Ангелина. Листы: 1 Модель · 2 Расписание-сетка · 3 Педагоги · 4 Студии и кластеры · 5 Конкуренты · 6 Было → Предлагаем · 7 Материалы и картинки · 8 Открытые вопросы · 9 Цены</t>
-        </is>
-      </c>
-    </row>
+          <t>20.09.2026 · Ангелина. Листы: 1 Модель · 2 Расписание-сетка · 3 Педагоги · 4 Студии и районы · 5 Конкуренты · 6 Было → Предлагаем · 7 Материалы и картинки · 8 Открытые вопросы · 9 Цены</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -655,6 +656,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
@@ -672,21 +674,21 @@
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>2. Сетка слотов: каждая студия — СБ 17:00 мастерская, ВС 17:00 МК (Новаторская/Алтуфьево 18:00). Хабы (Отрадное 27, Братиславская, Алтуфьево) — ещё будни 19:00. Кафе — СБ 15:00.</t>
+          <t>2. Сетка слотов: каждая студия — СБ 17:00 мастерская, ВС 17:00 МК (Новаторская/Алтуфьево 18:00). Главная студия районаы (Отрадное 27, Братиславская, Алтуфьево) — ещё будни 19:00. Кафе — СБ 15:00.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t>3. Проводим при 2+. За 48 ч (Т-2) в слоте &lt;2 → клиенту 3 варианта: тот же МК в хабе кластера / через неделю здесь / индивидуально 6000. Не отменяем — переносим.</t>
+          <t>3. Проводим при 2+. За 48 ч (Т-2) в слоте &lt;2 → клиенту 3 варианта: тот же МК в главной студии района района / через неделю здесь / индивидуально 6000. Не отменяем — переносим.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="10" t="inlineStr">
         <is>
-          <t>4. Педагог назначается на кластер (Север / Восток / Запад / Юго-Запад), а не на студию; при объединении едет в хаб. Мастерскую ведёт педагог своей студии.</t>
+          <t>4. Педагог назначается на район (Север / Восток / Запад / Юго-Запад), а не на студию; при объединении едет в главную студию района. Мастерскую ведёт педагог своей студии.</t>
         </is>
       </c>
     </row>
@@ -727,6 +729,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -1211,6 +1215,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -1597,12 +1602,15 @@
       </c>
       <c r="B13" s="27" t="inlineStr">
         <is>
-          <t>Правило 5. Кластеры и хабы</t>
+          <t>Правило 5. Районы и главная студия района</t>
         </is>
       </c>
       <c r="C13" s="26" t="inlineStr">
         <is>
-          <t>Студии сгруппированы по районам, чтобы переезд при объединении был ≤20 минут. Север: Отрадное 27, Отрадное 20к3, Алтуфьево, Яхромская → собираем в Отрадном 27 или Алтуфьево (10 мольбертов). Восток: Братиславская, Новокосино, Перово → в Братиславской (новое большое помещение). Запад: Полежаевская. Юго-Запад: Новаторская. Зеленоград — сам по себе.</t>
+          <t>Студии сгруппированы по районам. В каждом районе выбрана ГЛАВНАЯ СТУДИЯ — самая большая и удобная по дороге из соседних. Если в маленьких студиях района группы не набрались, людей приглашаем в главную студию района: ехать не больше 20 минут.
+Север: Отрадное 27, Отрадное 20к3, Алтуфьево, Яхромская → главная: Отрадное 27 (или Алтуфьево, там 10 мольбертов).
+Восток: Братиславская, Новокосино, Перово → главная: Братиславская (новое большое помещение).
+Запад: Полежаевская — сама по себе. Юго-Запад: Новаторская — сама по себе. Зеленоград — далеко, объединять не с кем.</t>
         </is>
       </c>
       <c r="D13" s="26" t="inlineStr">
@@ -1639,12 +1647,12 @@
       </c>
       <c r="B14" s="27" t="inlineStr">
         <is>
-          <t>Правило 6. Педагог — на кластер</t>
+          <t>Правило 6. Педагог — на район</t>
         </is>
       </c>
       <c r="C14" s="26" t="inlineStr">
         <is>
-          <t>На выходные назначаем 3–4 МК-педагога, по одному на кластер, а не по одному на студию. Если группы объединились — педагог едет в хаб. Мастерскую в субботу ведёт педагог самой студии после своих занятий.</t>
+          <t>На выходные назначаем 3–4 МК-педагога, по одному на район, а не по одному на студию. Если группы объединились — педагог едет в главную студию района. Мастерскую в субботу ведёт педагог самой студии после своих занятий.</t>
         </is>
       </c>
       <c r="D14" s="26" t="inlineStr">
@@ -1654,7 +1662,7 @@
       </c>
       <c r="E14" s="26" t="inlineStr">
         <is>
-          <t>Проверенных МК-педагогов всего трое — на 10 студий не хватит, на 4 кластера хватит.</t>
+          <t>Проверенных МК-педагогов всего трое — на 10 студий не хватит, на 4 района хватит.</t>
         </is>
       </c>
       <c r="F14" s="26" t="inlineStr">
@@ -1733,7 +1741,7 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>ЧТ 9.10 19:00 — МК в Отрадном 27 (будни, хаб). СБ 11.10 15:00 — МК в «Бухаре». СБ 17:00 — мастерская «шоперы» в 9 студиях. ВС 12.10 17:00 — МК «Домик в горах» в 9 студиях; за 48 ч смотрим набор: где 1 человек — предлагаем хаб кластера.</t>
+          <t>ЧТ 9.10 19:00 — МК в Отрадном 27 (будни, главная студия района). СБ 11.10 15:00 — МК в «Бухаре». СБ 17:00 — мастерская «шоперы» в 9 студиях. ВС 12.10 17:00 — МК «Домик в горах» в 9 студиях; за 48 ч смотрим набор: где 1 человек — предлагаем главную студию района.</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -1796,10 +1804,11 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>Одна тема на выходные во всех студиях. СБ — мастерская у себя (педагог локации), ВС — МК (педагог кластера). При &lt;2 записей за 48 ч — объединяем в хаб кластера или переносим на неделю. Записей и статус — ведутся в штабе.</t>
-        </is>
-      </c>
-    </row>
+          <t>Одна тема на выходные во всех студиях. СБ — мастерская у себя (педагог локации), ВС — МК (педагог района). При &lt;2 записей за 48 ч — объединяем в главную студию района или переносим на неделю. Записей и статус — ведутся в штабе.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -1818,7 +1827,7 @@
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Кластер</t>
+          <t>Район</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
@@ -1890,7 +1899,7 @@
       </c>
       <c r="E5" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F5" s="16" t="inlineStr">
@@ -1930,7 +1939,7 @@
       </c>
       <c r="M5" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -1993,7 +2002,7 @@
       </c>
       <c r="M6" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2029,7 @@
       </c>
       <c r="E7" s="16" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F7" s="16" t="inlineStr">
@@ -2060,7 +2069,7 @@
       </c>
       <c r="M7" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2132,7 @@
       </c>
       <c r="M8" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2159,7 @@
       </c>
       <c r="E9" s="16" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F9" s="16" t="inlineStr">
@@ -2190,7 +2199,7 @@
       </c>
       <c r="M9" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -2253,7 +2262,7 @@
       </c>
       <c r="M10" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2289,7 @@
       </c>
       <c r="E11" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F11" s="16" t="inlineStr">
@@ -2320,7 +2329,7 @@
       </c>
       <c r="M11" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2356,7 @@
       </c>
       <c r="E12" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F12" s="16" t="inlineStr">
@@ -2387,7 +2396,7 @@
       </c>
       <c r="M12" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2463,7 @@
       </c>
       <c r="M13" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2490,7 @@
       </c>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F14" s="17" t="inlineStr">
@@ -2611,7 +2620,7 @@
       </c>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F16" s="17" t="inlineStr">
@@ -2741,7 +2750,7 @@
       </c>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F18" s="17" t="inlineStr">
@@ -2938,7 +2947,7 @@
       </c>
       <c r="E21" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F21" s="17" t="inlineStr">
@@ -3005,7 +3014,7 @@
       </c>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F22" s="17" t="inlineStr">
@@ -3139,7 +3148,7 @@
       </c>
       <c r="E24" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F24" s="16" t="inlineStr">
@@ -3179,7 +3188,7 @@
       </c>
       <c r="M24" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -3242,7 +3251,7 @@
       </c>
       <c r="M25" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -3269,7 +3278,7 @@
       </c>
       <c r="E26" s="16" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F26" s="16" t="inlineStr">
@@ -3309,7 +3318,7 @@
       </c>
       <c r="M26" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -3372,7 +3381,7 @@
       </c>
       <c r="M27" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3408,7 @@
       </c>
       <c r="E28" s="16" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F28" s="16" t="inlineStr">
@@ -3439,7 +3448,7 @@
       </c>
       <c r="M28" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3511,7 @@
       </c>
       <c r="M29" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3538,7 @@
       </c>
       <c r="E30" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F30" s="16" t="inlineStr">
@@ -3569,7 +3578,7 @@
       </c>
       <c r="M30" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3605,7 @@
       </c>
       <c r="E31" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F31" s="16" t="inlineStr">
@@ -3636,7 +3645,7 @@
       </c>
       <c r="M31" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3712,7 @@
       </c>
       <c r="M32" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3739,7 @@
       </c>
       <c r="E33" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F33" s="17" t="inlineStr">
@@ -3860,7 +3869,7 @@
       </c>
       <c r="E35" s="17" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F35" s="17" t="inlineStr">
@@ -3990,7 +3999,7 @@
       </c>
       <c r="E37" s="17" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F37" s="17" t="inlineStr">
@@ -4187,7 +4196,7 @@
       </c>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F40" s="17" t="inlineStr">
@@ -4254,7 +4263,7 @@
       </c>
       <c r="E41" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F41" s="17" t="inlineStr">
@@ -4455,7 +4464,7 @@
       </c>
       <c r="E44" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F44" s="16" t="inlineStr">
@@ -4495,7 +4504,7 @@
       </c>
       <c r="M44" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4567,7 @@
       </c>
       <c r="M45" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -4585,7 +4594,7 @@
       </c>
       <c r="E46" s="16" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F46" s="16" t="inlineStr">
@@ -4625,7 +4634,7 @@
       </c>
       <c r="M46" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4697,7 @@
       </c>
       <c r="M47" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4724,7 @@
       </c>
       <c r="E48" s="16" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F48" s="16" t="inlineStr">
@@ -4755,7 +4764,7 @@
       </c>
       <c r="M48" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4827,7 @@
       </c>
       <c r="M49" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -4845,7 +4854,7 @@
       </c>
       <c r="E50" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F50" s="16" t="inlineStr">
@@ -4885,7 +4894,7 @@
       </c>
       <c r="M50" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -4912,7 +4921,7 @@
       </c>
       <c r="E51" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F51" s="16" t="inlineStr">
@@ -4952,7 +4961,7 @@
       </c>
       <c r="M51" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5028,7 @@
       </c>
       <c r="M52" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5055,7 @@
       </c>
       <c r="E53" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F53" s="17" t="inlineStr">
@@ -5176,7 +5185,7 @@
       </c>
       <c r="E55" s="17" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F55" s="17" t="inlineStr">
@@ -5306,7 +5315,7 @@
       </c>
       <c r="E57" s="17" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F57" s="17" t="inlineStr">
@@ -5503,7 +5512,7 @@
       </c>
       <c r="E60" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F60" s="17" t="inlineStr">
@@ -5570,7 +5579,7 @@
       </c>
       <c r="E61" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F61" s="17" t="inlineStr">
@@ -5771,7 +5780,7 @@
       </c>
       <c r="E64" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F64" s="16" t="inlineStr">
@@ -5811,7 +5820,7 @@
       </c>
       <c r="M64" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5883,7 @@
       </c>
       <c r="M65" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5910,7 @@
       </c>
       <c r="E66" s="16" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F66" s="16" t="inlineStr">
@@ -5941,7 +5950,7 @@
       </c>
       <c r="M66" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6013,7 @@
       </c>
       <c r="M67" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -6031,7 +6040,7 @@
       </c>
       <c r="E68" s="16" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F68" s="16" t="inlineStr">
@@ -6071,7 +6080,7 @@
       </c>
       <c r="M68" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -6134,7 +6143,7 @@
       </c>
       <c r="M69" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -6161,7 +6170,7 @@
       </c>
       <c r="E70" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F70" s="16" t="inlineStr">
@@ -6201,7 +6210,7 @@
       </c>
       <c r="M70" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -6228,7 +6237,7 @@
       </c>
       <c r="E71" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F71" s="16" t="inlineStr">
@@ -6268,7 +6277,7 @@
       </c>
       <c r="M71" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -6335,7 +6344,7 @@
       </c>
       <c r="M72" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -6362,7 +6371,7 @@
       </c>
       <c r="E73" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F73" s="17" t="inlineStr">
@@ -6492,7 +6501,7 @@
       </c>
       <c r="E75" s="17" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F75" s="17" t="inlineStr">
@@ -6622,7 +6631,7 @@
       </c>
       <c r="E77" s="17" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F77" s="17" t="inlineStr">
@@ -6819,7 +6828,7 @@
       </c>
       <c r="E80" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F80" s="17" t="inlineStr">
@@ -6886,7 +6895,7 @@
       </c>
       <c r="E81" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F81" s="17" t="inlineStr">
@@ -7087,7 +7096,7 @@
       </c>
       <c r="E84" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F84" s="16" t="inlineStr">
@@ -7127,7 +7136,7 @@
       </c>
       <c r="M84" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -7190,7 +7199,7 @@
       </c>
       <c r="M85" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -7217,7 +7226,7 @@
       </c>
       <c r="E86" s="16" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F86" s="16" t="inlineStr">
@@ -7257,7 +7266,7 @@
       </c>
       <c r="M86" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -7320,7 +7329,7 @@
       </c>
       <c r="M87" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7356,7 @@
       </c>
       <c r="E88" s="16" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F88" s="16" t="inlineStr">
@@ -7387,7 +7396,7 @@
       </c>
       <c r="M88" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -7450,7 +7459,7 @@
       </c>
       <c r="M89" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7486,7 @@
       </c>
       <c r="E90" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F90" s="16" t="inlineStr">
@@ -7517,7 +7526,7 @@
       </c>
       <c r="M90" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7553,7 @@
       </c>
       <c r="E91" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F91" s="16" t="inlineStr">
@@ -7584,7 +7593,7 @@
       </c>
       <c r="M91" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -7651,7 +7660,7 @@
       </c>
       <c r="M92" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7687,7 @@
       </c>
       <c r="E93" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F93" s="17" t="inlineStr">
@@ -7808,7 +7817,7 @@
       </c>
       <c r="E95" s="17" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F95" s="17" t="inlineStr">
@@ -7938,7 +7947,7 @@
       </c>
       <c r="E97" s="17" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F97" s="17" t="inlineStr">
@@ -8135,7 +8144,7 @@
       </c>
       <c r="E100" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F100" s="17" t="inlineStr">
@@ -8202,7 +8211,7 @@
       </c>
       <c r="E101" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F101" s="17" t="inlineStr">
@@ -8403,7 +8412,7 @@
       </c>
       <c r="E104" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F104" s="16" t="inlineStr">
@@ -8443,7 +8452,7 @@
       </c>
       <c r="M104" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8515,7 @@
       </c>
       <c r="M105" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -8533,7 +8542,7 @@
       </c>
       <c r="E106" s="16" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F106" s="16" t="inlineStr">
@@ -8573,7 +8582,7 @@
       </c>
       <c r="M106" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8645,7 @@
       </c>
       <c r="M107" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -8663,7 +8672,7 @@
       </c>
       <c r="E108" s="16" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F108" s="16" t="inlineStr">
@@ -8703,7 +8712,7 @@
       </c>
       <c r="M108" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -8766,7 +8775,7 @@
       </c>
       <c r="M109" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8802,7 @@
       </c>
       <c r="E110" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F110" s="16" t="inlineStr">
@@ -8833,7 +8842,7 @@
       </c>
       <c r="M110" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -8860,7 +8869,7 @@
       </c>
       <c r="E111" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F111" s="16" t="inlineStr">
@@ -8900,7 +8909,7 @@
       </c>
       <c r="M111" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -8967,7 +8976,7 @@
       </c>
       <c r="M112" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -8994,7 +9003,7 @@
       </c>
       <c r="E113" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F113" s="17" t="inlineStr">
@@ -9124,7 +9133,7 @@
       </c>
       <c r="E115" s="17" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F115" s="17" t="inlineStr">
@@ -9254,7 +9263,7 @@
       </c>
       <c r="E117" s="17" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F117" s="17" t="inlineStr">
@@ -9451,7 +9460,7 @@
       </c>
       <c r="E120" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F120" s="17" t="inlineStr">
@@ -9518,7 +9527,7 @@
       </c>
       <c r="E121" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F121" s="17" t="inlineStr">
@@ -9719,7 +9728,7 @@
       </c>
       <c r="E124" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F124" s="16" t="inlineStr">
@@ -9759,7 +9768,7 @@
       </c>
       <c r="M124" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9831,7 @@
       </c>
       <c r="M125" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -9849,7 +9858,7 @@
       </c>
       <c r="E126" s="16" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F126" s="16" t="inlineStr">
@@ -9889,7 +9898,7 @@
       </c>
       <c r="M126" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -9952,7 +9961,7 @@
       </c>
       <c r="M127" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -9979,7 +9988,7 @@
       </c>
       <c r="E128" s="16" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F128" s="16" t="inlineStr">
@@ -10019,7 +10028,7 @@
       </c>
       <c r="M128" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -10082,7 +10091,7 @@
       </c>
       <c r="M129" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -10109,7 +10118,7 @@
       </c>
       <c r="E130" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F130" s="16" t="inlineStr">
@@ -10149,7 +10158,7 @@
       </c>
       <c r="M130" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -10176,7 +10185,7 @@
       </c>
       <c r="E131" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F131" s="16" t="inlineStr">
@@ -10216,7 +10225,7 @@
       </c>
       <c r="M131" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -10283,7 +10292,7 @@
       </c>
       <c r="M132" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -10310,7 +10319,7 @@
       </c>
       <c r="E133" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F133" s="17" t="inlineStr">
@@ -10440,7 +10449,7 @@
       </c>
       <c r="E135" s="17" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F135" s="17" t="inlineStr">
@@ -10570,7 +10579,7 @@
       </c>
       <c r="E137" s="17" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F137" s="17" t="inlineStr">
@@ -10767,7 +10776,7 @@
       </c>
       <c r="E140" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F140" s="17" t="inlineStr">
@@ -10834,7 +10843,7 @@
       </c>
       <c r="E141" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F141" s="17" t="inlineStr">
@@ -11035,7 +11044,7 @@
       </c>
       <c r="E144" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F144" s="16" t="inlineStr">
@@ -11075,7 +11084,7 @@
       </c>
       <c r="M144" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -11138,7 +11147,7 @@
       </c>
       <c r="M145" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -11165,7 +11174,7 @@
       </c>
       <c r="E146" s="16" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F146" s="16" t="inlineStr">
@@ -11205,7 +11214,7 @@
       </c>
       <c r="M146" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -11268,7 +11277,7 @@
       </c>
       <c r="M147" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -11295,7 +11304,7 @@
       </c>
       <c r="E148" s="16" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F148" s="16" t="inlineStr">
@@ -11335,7 +11344,7 @@
       </c>
       <c r="M148" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -11398,7 +11407,7 @@
       </c>
       <c r="M149" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -11425,7 +11434,7 @@
       </c>
       <c r="E150" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F150" s="16" t="inlineStr">
@@ -11465,7 +11474,7 @@
       </c>
       <c r="M150" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -11492,7 +11501,7 @@
       </c>
       <c r="E151" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F151" s="16" t="inlineStr">
@@ -11532,7 +11541,7 @@
       </c>
       <c r="M151" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -11599,7 +11608,7 @@
       </c>
       <c r="M152" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -11626,7 +11635,7 @@
       </c>
       <c r="E153" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F153" s="17" t="inlineStr">
@@ -11756,7 +11765,7 @@
       </c>
       <c r="E155" s="17" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F155" s="17" t="inlineStr">
@@ -11886,7 +11895,7 @@
       </c>
       <c r="E157" s="17" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F157" s="17" t="inlineStr">
@@ -12083,7 +12092,7 @@
       </c>
       <c r="E160" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F160" s="17" t="inlineStr">
@@ -12150,7 +12159,7 @@
       </c>
       <c r="E161" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F161" s="17" t="inlineStr">
@@ -12351,7 +12360,7 @@
       </c>
       <c r="E164" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F164" s="16" t="inlineStr">
@@ -12391,7 +12400,7 @@
       </c>
       <c r="M164" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -12454,7 +12463,7 @@
       </c>
       <c r="M165" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12490,7 @@
       </c>
       <c r="E166" s="16" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F166" s="16" t="inlineStr">
@@ -12521,7 +12530,7 @@
       </c>
       <c r="M166" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -12584,7 +12593,7 @@
       </c>
       <c r="M167" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -12611,7 +12620,7 @@
       </c>
       <c r="E168" s="16" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F168" s="16" t="inlineStr">
@@ -12651,7 +12660,7 @@
       </c>
       <c r="M168" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -12714,7 +12723,7 @@
       </c>
       <c r="M169" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -12741,7 +12750,7 @@
       </c>
       <c r="E170" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F170" s="16" t="inlineStr">
@@ -12781,7 +12790,7 @@
       </c>
       <c r="M170" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -12808,7 +12817,7 @@
       </c>
       <c r="E171" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F171" s="16" t="inlineStr">
@@ -12848,7 +12857,7 @@
       </c>
       <c r="M171" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -12915,7 +12924,7 @@
       </c>
       <c r="M172" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -12942,7 +12951,7 @@
       </c>
       <c r="E173" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F173" s="17" t="inlineStr">
@@ -13072,7 +13081,7 @@
       </c>
       <c r="E175" s="17" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F175" s="17" t="inlineStr">
@@ -13202,7 +13211,7 @@
       </c>
       <c r="E177" s="17" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F177" s="17" t="inlineStr">
@@ -13399,7 +13408,7 @@
       </c>
       <c r="E180" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F180" s="17" t="inlineStr">
@@ -13466,7 +13475,7 @@
       </c>
       <c r="E181" s="17" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F181" s="17" t="inlineStr">
@@ -13667,7 +13676,7 @@
       </c>
       <c r="E184" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F184" s="16" t="inlineStr">
@@ -13707,7 +13716,7 @@
       </c>
       <c r="M184" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -13770,7 +13779,7 @@
       </c>
       <c r="M185" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -13797,7 +13806,7 @@
       </c>
       <c r="E186" s="16" t="inlineStr">
         <is>
-          <t>хаб (10 мольб.)</t>
+          <t>главная студия района (10 мольбертов)</t>
         </is>
       </c>
       <c r="F186" s="16" t="inlineStr">
@@ -13837,7 +13846,7 @@
       </c>
       <c r="M186" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -13900,7 +13909,7 @@
       </c>
       <c r="M187" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -13927,7 +13936,7 @@
       </c>
       <c r="E188" s="16" t="inlineStr">
         <is>
-          <t>хаб (новое большое)</t>
+          <t>главная студия района (новое большое помещение)</t>
         </is>
       </c>
       <c r="F188" s="16" t="inlineStr">
@@ -13967,7 +13976,7 @@
       </c>
       <c r="M188" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -14030,7 +14039,7 @@
       </c>
       <c r="M189" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -14057,7 +14066,7 @@
       </c>
       <c r="E190" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F190" s="16" t="inlineStr">
@@ -14097,7 +14106,7 @@
       </c>
       <c r="M190" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -14124,7 +14133,7 @@
       </c>
       <c r="E191" s="16" t="inlineStr">
         <is>
-          <t>хаб</t>
+          <t>главная студия района</t>
         </is>
       </c>
       <c r="F191" s="16" t="inlineStr">
@@ -14164,7 +14173,7 @@
       </c>
       <c r="M191" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -14231,7 +14240,7 @@
       </c>
       <c r="M192" s="16" t="inlineStr">
         <is>
-          <t>🟡 педагог кластера не подтверждён</t>
+          <t>🟡 педагог района не подтверждён</t>
         </is>
       </c>
     </row>
@@ -14269,6 +14278,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -14359,7 +14370,7 @@
       </c>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>МК-педагог кластера Север (+ подмена ЮЗ), кафе СБ</t>
+          <t>МК-педагог района Север (+ подмена ЮЗ), кафе СБ</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -14411,7 +14422,7 @@
       </c>
       <c r="H6" s="13" t="inlineStr">
         <is>
-          <t>МК-педагог кластера Восток (+ ЮЗ), кафе СБ</t>
+          <t>МК-педагог района Восток (+ ЮЗ), кафе СБ</t>
         </is>
       </c>
       <c r="I6" s="13" t="inlineStr">
@@ -14567,7 +14578,7 @@
       </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
-          <t>будни 19:00 в хабе Отрадное</t>
+          <t>будни 19:00 в главной студии района Отрадное</t>
         </is>
       </c>
       <c r="I9" s="19" t="inlineStr">
@@ -15183,10 +15194,12 @@
     <row r="1">
       <c r="A1" s="11" t="inlineStr">
         <is>
-          <t>Студии: адрес, кластер, вместимость, свободное время по выходным, материалы</t>
-        </is>
-      </c>
-    </row>
+          <t>Студии: адрес, район, вместимость, свободное время по выходным, материалы</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -15200,12 +15213,12 @@
       </c>
       <c r="C4" s="12" t="inlineStr">
         <is>
-          <t>Кластер</t>
+          <t>Район</t>
         </is>
       </c>
       <c r="D4" s="12" t="inlineStr">
         <is>
-          <t>Хаб?</t>
+          <t>Главная студия района?</t>
         </is>
       </c>
       <c r="E4" s="12" t="inlineStr">
@@ -15262,7 +15275,7 @@
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>✅ хаб</t>
+          <t>✅ главная студия района</t>
         </is>
       </c>
       <c r="E5" s="19" t="inlineStr">
@@ -15372,7 +15385,7 @@
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>✅ хаб (большой)</t>
+          <t>✅ главная студия района (большая)</t>
         </is>
       </c>
       <c r="E7" s="19" t="inlineStr">
@@ -15478,7 +15491,7 @@
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>✅ хаб</t>
+          <t>✅ главная студия района</t>
         </is>
       </c>
       <c r="E9" s="19" t="inlineStr">
@@ -15641,7 +15654,7 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
-          <t>✅ хаб</t>
+          <t>✅ главная студия района</t>
         </is>
       </c>
       <c r="E12" s="19" t="inlineStr">
@@ -15694,7 +15707,7 @@
       </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
-          <t>✅ хаб</t>
+          <t>✅ главная студия района</t>
         </is>
       </c>
       <c r="E13" s="19" t="inlineStr">
@@ -16051,6 +16064,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -16599,6 +16614,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -16639,7 +16656,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>Сетка на месяц вперёд: СБ мастерская + ВС МК в каждой студии, будни 19:00 в хабах, кафе СБ днём.</t>
+          <t>Сетка на месяц вперёд: СБ мастерская + ВС МК в каждой студии, будни 19:00 в главных студиях районов, кафе СБ днём.</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -16720,7 +16737,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>Проводим при 2+; при &lt;2 за 48 ч — перенос в хаб / на неделю / индивидуально</t>
+          <t>Проводим при 2+; при &lt;2 за 48 ч — перенос в главная студия района / на неделю / индивидуально</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -16828,7 +16845,7 @@
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>3 проверенных — на кластеры; педагоги локаций — мастерские; донабор в октябре, стажировка на МК</t>
+          <t>3 проверенных — на районы; педагоги локаций — мастерские; донабор в октябре, стажировка на МК</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
@@ -16980,6 +16997,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -17490,6 +17509,8 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -17978,7 +17999,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>Будни 19:00 в хабах (Отрадное 27, Братиславская, Алтуфьево)</t>
+          <t>Будни 19:00 в главных студиях районов (Отрадное 27, Братиславская, Алтуфьево)</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
